--- a/data/trans_camb/P1429-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1429-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; -0,25</t>
+          <t>-2,22; -0,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; -0,3</t>
+          <t>-2,31; -0,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,72</t>
+          <t>-1,48; 0,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,94</t>
+          <t>-2,9; 0,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 2,49</t>
+          <t>-2,0; 2,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,07</t>
+          <t>-0,04; 3,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,04</t>
+          <t>-2,08; 0,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,77</t>
+          <t>-1,56; 0,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,08</t>
+          <t>-0,26; 1,97</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-23,11%</t>
+          <t>-25,63%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 7,76</t>
+          <t>-100,0; 54,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 12,26</t>
+          <t>-100,0; 6,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,56; 98,26</t>
+          <t>-68,93; 111,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,38; 39,47</t>
+          <t>-62,12; 40,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,45; 99,91</t>
+          <t>-41,52; 89,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 160,53</t>
+          <t>-3,1; 139,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-67,86; 4,99</t>
+          <t>-67,77; 7,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 39,43</t>
+          <t>-52,95; 39,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 102,16</t>
+          <t>-9,56; 102,59</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,63</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; -0,66</t>
+          <t>-2,32; -0,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; -0,23</t>
+          <t>-1,85; -0,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,1</t>
+          <t>-1,5; 0,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,6</t>
+          <t>-1,81; 1,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,27</t>
+          <t>-2,05; 1,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,97</t>
+          <t>-1,01; 1,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,25</t>
+          <t>-1,62; 0,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,4</t>
+          <t>-1,64; 0,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,57</t>
+          <t>-0,98; 0,84</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-48,69%</t>
+          <t>-37,08%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-11,3%</t>
+          <t>-0,06%</t>
         </is>
       </c>
     </row>
@@ -1004,42 +1004,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-92,77; -3,81</t>
+          <t>-93,33; 1,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-83,87; 16,04</t>
+          <t>-75,39; 61,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 56,23</t>
+          <t>-39,02; 60,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,71; 43,38</t>
+          <t>-43,42; 55,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 69,54</t>
+          <t>-21,79; 65,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,27; 13,39</t>
+          <t>-52,98; 10,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,29; 23,47</t>
+          <t>-52,11; 18,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,91; 28,24</t>
+          <t>-30,46; 41,43</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,36</t>
+          <t>-1,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-0,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,11</t>
+          <t>-0,55; 0,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,44</t>
+          <t>-0,66; 0,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,92</t>
+          <t>-0,42; 1,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,4; -0,12</t>
+          <t>-4,5; 0,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 0,37</t>
+          <t>-4,29; 0,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; -0,2</t>
+          <t>-3,38; 0,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; -0,07</t>
+          <t>-2,52; -0,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,27</t>
+          <t>-2,12; 0,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,29</t>
+          <t>-1,73; 0,5</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-41,3%</t>
+          <t>-21,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-29,14%</t>
+          <t>-16,77%</t>
         </is>
       </c>
     </row>
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,19; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,33; -0,79</t>
+          <t>-64,79; 4,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,27; 11,11</t>
+          <t>-59,33; 9,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,8; -4,28</t>
+          <t>-47,7; 17,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-63,44; -1,93</t>
+          <t>-65,38; 0,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,66; 13,19</t>
+          <t>-55,77; 14,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,1; 10,43</t>
+          <t>-44,64; 24,01</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; -0,18</t>
+          <t>-1,6; -0,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,14</t>
+          <t>-1,36; 0,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,56</t>
+          <t>-0,85; 1,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,46</t>
+          <t>-0,44; 3,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,16</t>
+          <t>-3,2; 0,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,82</t>
+          <t>-1,09; 2,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,5</t>
+          <t>-0,63; 1,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; -0,2</t>
+          <t>-1,92; -0,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,21</t>
+          <t>-0,61; 1,35</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>-4,91%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 22,72</t>
+          <t>-100,0; 19,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-89,48; 61,43</t>
+          <t>-91,55; 33,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,8; 264,57</t>
+          <t>-70,43; 242,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 94,57</t>
+          <t>-8,86; 102,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,86; 7,85</t>
+          <t>-62,09; 3,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 57,61</t>
+          <t>-20,86; 62,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,75; 67,21</t>
+          <t>-19,09; 71,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-61,67; -6,77</t>
+          <t>-60,35; -0,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 56,0</t>
+          <t>-19,19; 59,98</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>0,16</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; -0,45</t>
+          <t>-1,25; -0,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; -0,31</t>
+          <t>-1,11; -0,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,28</t>
+          <t>-0,68; 0,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,72</t>
+          <t>-1,32; 0,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,12</t>
+          <t>-1,73; 0,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,97</t>
+          <t>-0,45; 1,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; -0,05</t>
+          <t>-1,04; -0,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; -0,24</t>
+          <t>-1,25; -0,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,48</t>
+          <t>-0,4; 0,67</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-20,56%</t>
+          <t>-18,92%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,21%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-94,18; -46,04</t>
+          <t>-94,18; -45,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-84,58; -37,68</t>
+          <t>-84,24; -37,78</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,99; 39,75</t>
+          <t>-52,1; 37,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 19,04</t>
+          <t>-27,57; 20,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 3,73</t>
+          <t>-36,49; 5,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 25,27</t>
+          <t>-9,18; 38,63</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-39,21; -1,65</t>
+          <t>-35,85; -1,22</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,88; -10,37</t>
+          <t>-42,02; -10,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 20,06</t>
+          <t>-13,4; 29,4</t>
         </is>
       </c>
     </row>
